--- a/measurements/29/Filled_2D_sections/coronal/week29_coronal_Batch_Allmarks.xlsx
+++ b/measurements/29/Filled_2D_sections/coronal/week29_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +616,76 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.582391433670435</v>
+        <v>2509.07029478458</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68040315116324</v>
+        <v>325.6650139036632</v>
       </c>
       <c r="E2" t="n">
-        <v>11.44051129062001</v>
+        <v>223.3623632930574</v>
       </c>
       <c r="F2" t="n">
         <v>1.458012035252251</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2972901245355266</v>
+        <v>0.2972901245355265</v>
       </c>
       <c r="H2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.964285714285714</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.47619047619047</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.40189200680272</v>
+      </c>
+      <c r="L2" t="n">
         <v>3</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.5378239329268293</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.048780487804878</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.7512068089430896</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>20.47619047619047</v>
+      </c>
+      <c r="N2" t="n">
+        <v>13.02269345238095</v>
+      </c>
+      <c r="O2" t="n">
+        <v>10.50037202380952</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.186755952380952</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.853422619047619</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.964285714285714</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>6.550118976799524</v>
+      <c r="AK2" s="2" t="n">
+        <v>2496.768707482993</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +696,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.606186793575253</v>
+        <v>2518.140589569161</v>
       </c>
       <c r="D3" t="n">
-        <v>16.64345883160103</v>
+        <v>324.9437200455438</v>
       </c>
       <c r="E3" t="n">
-        <v>11.41193634126244</v>
+        <v>222.8044714246477</v>
       </c>
       <c r="F3" t="n">
         <v>1.45842548835668</v>
@@ -572,24 +715,57 @@
         <v>0.2996908898612742</v>
       </c>
       <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.531622023809524</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.47619047619047</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.452912414965986</v>
+      </c>
+      <c r="L3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.5362995426829269</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.048780487804878</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7499364837398375</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>20.47619047619047</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12.97805059523809</v>
+      </c>
+      <c r="O3" t="n">
+        <v>10.47061011904762</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6.40625</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.604910714285714</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.702752976190476</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.531622023809524</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>15.69215730704913</v>
+      <c r="AK3" s="2" t="n">
+        <v>306.3706902804828</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +776,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.667459845330161</v>
+        <v>2541.496598639455</v>
       </c>
       <c r="D4" t="n">
-        <v>16.59958097992874</v>
+        <v>324.0870572271801</v>
       </c>
       <c r="E4" t="n">
-        <v>11.46071682615978</v>
+        <v>223.7568523202623</v>
       </c>
       <c r="F4" t="n">
         <v>1.448389418543105</v>
@@ -619,24 +795,54 @@
         <v>0.3040717139744891</v>
       </c>
       <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.4453125</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.80654761904762</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.201388888888888</v>
+      </c>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.5435403963414634</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.014481707317073</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.73828125</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>19.80654761904762</v>
+      </c>
+      <c r="N4" t="n">
+        <v>12.82366071428571</v>
+      </c>
+      <c r="O4" t="n">
+        <v>10.61197916666667</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8.119419642857142</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.40141369047619</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.4453125</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>11.40861831903458</v>
+      <c r="AK4" s="2" t="n">
+        <v>222.7396909906751</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +853,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.659131469363475</v>
+        <v>2538.321995464853</v>
       </c>
       <c r="D5" t="n">
-        <v>16.88389452492319</v>
+        <v>329.6379407246907</v>
       </c>
       <c r="E5" t="n">
-        <v>11.43459321522131</v>
+        <v>223.2468199162256</v>
       </c>
       <c r="F5" t="n">
         <v>1.47656276066279</v>
@@ -666,23 +872,50 @@
         <v>0.293550072732533</v>
       </c>
       <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.273065476190476</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.87648809523809</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.711371527777777</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.5203887195121951</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.966844512195122</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.6872856326219512</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="n">
+        <v>10.15997023809524</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>18.87648809523809</v>
+      </c>
+      <c r="R5" t="n">
+        <v>13.41843377976191</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.321428571428571</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.273065476190476</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>1.375409813240295</v>
       </c>
     </row>
@@ -694,42 +927,72 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.685901249256395</v>
+        <v>2548.526077097506</v>
       </c>
       <c r="D6" t="n">
-        <v>16.70897813831888</v>
+        <v>326.2229065100352</v>
       </c>
       <c r="E6" t="n">
-        <v>11.45479876820634</v>
+        <v>223.6413092840286</v>
       </c>
       <c r="F6" t="n">
         <v>1.45868805523637</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3009331562999281</v>
+        <v>0.3009331562999282</v>
       </c>
       <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.595982142857143</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.20498511904762</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.48453443877551</v>
+      </c>
+      <c r="L6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.5365853658536586</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.9324504573170732</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.6783774771341464</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>10.47619047619048</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>18.20498511904762</v>
+      </c>
+      <c r="R6" t="n">
+        <v>13.24451264880952</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.4609375</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.356770833333333</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.595982142857143</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>0.3358723979844039</v>
       </c>
     </row>
@@ -741,43 +1004,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.683224271267103</v>
+        <v>2547.50566893424</v>
       </c>
       <c r="D7" t="n">
-        <v>16.51630750225812</v>
+        <v>322.4612417107537</v>
       </c>
       <c r="E7" t="n">
-        <v>11.46071682906732</v>
+        <v>223.7568523770287</v>
       </c>
       <c r="F7" t="n">
         <v>1.441123426099187</v>
       </c>
       <c r="G7" t="n">
-        <v>0.307871848409011</v>
+        <v>0.3078718484090109</v>
       </c>
       <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.824776785714286</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.60863095238095</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.373458758503402</v>
+      </c>
+      <c r="L7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.953125</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.6657298018292683</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>18.60863095238095</v>
+      </c>
+      <c r="R7" t="n">
+        <v>12.99758184523809</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.602306547619047</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.196800595238095</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.824776785714286</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>2.8</v>
+      <c r="AK7" s="2" t="n">
+        <v>7.15</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1081,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.684116597263534</v>
+        <v>2547.845804988662</v>
       </c>
       <c r="D8" t="n">
-        <v>15.99891229373653</v>
+        <v>312.3597162110465</v>
       </c>
       <c r="E8" t="n">
-        <v>11.36315584182739</v>
+        <v>221.8520902452015</v>
       </c>
       <c r="F8" t="n">
         <v>1.407963818893082</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3281504211060752</v>
+        <v>0.3281504211060753</v>
       </c>
       <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.059151785714286</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.09709821428571</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.192230017006802</v>
+      </c>
+      <c r="L8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.5062881097560976</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.9269245426829269</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.6402915396341464</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>9.884672619047619</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>18.09709821428571</v>
+      </c>
+      <c r="R8" t="n">
+        <v>12.50093005952381</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.859002976190476</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.423735119047619</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.059151785714286</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.5799780868902439</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.935081845238095</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1158,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.780190362879239</v>
+        <v>2584.467120181406</v>
       </c>
       <c r="D9" t="n">
-        <v>14.52264618001333</v>
+        <v>283.5373778002602</v>
       </c>
       <c r="E9" t="n">
-        <v>11.3833613802747</v>
+        <v>222.2465793291728</v>
       </c>
       <c r="F9" t="n">
         <v>1.275778365885707</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4039803472837745</v>
+        <v>0.4039803472837746</v>
       </c>
       <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.767857142857143</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12.35863095238095</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.643016581632653</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.5075266768292683</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6330030487804879</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5576410060975611</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>12.35863095238095</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10.39434523809524</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9.908854166666666</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.29203869047619</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.983630952380952</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.795758928571428</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.767857142857143</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.9441596798780487</v>
+      <c r="AK9" s="2" t="n">
+        <v>18.43359375</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1238,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.678167757287329</v>
+        <v>2545.578231292517</v>
       </c>
       <c r="D10" t="n">
-        <v>15.4874351780589</v>
+        <v>302.3737344287691</v>
       </c>
       <c r="E10" t="n">
-        <v>11.4178544137536</v>
+        <v>222.9200147447132</v>
       </c>
       <c r="F10" t="n">
         <v>1.356422548128062</v>
@@ -901,24 +1257,57 @@
         <v>0.3498711923970348</v>
       </c>
       <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.482514880952381</v>
+      </c>
+      <c r="J10" t="n">
+        <v>17.87016369047619</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.172154017857143</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>17.87016369047619</v>
+      </c>
+      <c r="R10" t="n">
+        <v>11.88662574404762</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.556547619047619</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.9153010670731707</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.6491679369918699</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="AA10" t="n">
+        <v>2.542782738095238</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.248883928571428</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.482514880952381</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7337700076219512</v>
+      <c r="AK10" s="2" t="n">
+        <v>8.030376408375849</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1318,76 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.630577037477692</v>
+        <v>2527.437641723356</v>
       </c>
       <c r="D11" t="n">
-        <v>15.60520169502351</v>
+        <v>304.6729854742686</v>
       </c>
       <c r="E11" t="n">
-        <v>11.31437538019041</v>
+        <v>220.8997098037175</v>
       </c>
       <c r="F11" t="n">
         <v>1.379236694086147</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3421546265645158</v>
+        <v>0.3421546265645159</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5095274390243902</v>
+        <v>2.44047619047619</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9155868902439025</v>
+        <v>17.87574404761905</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6572662601626017</v>
+        <v>7.526506696428571</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>17.87574404761905</v>
+      </c>
+      <c r="R11" t="n">
+        <v>12.00520833333333</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.643973214285714</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.413318452380952</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.693452380952381</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.44047619047619</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>3.05</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1398,79 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.604997025580012</v>
+        <v>2517.687074829932</v>
       </c>
       <c r="D12" t="n">
-        <v>15.41007974961909</v>
+        <v>300.8634617782774</v>
       </c>
       <c r="E12" t="n">
-        <v>11.43805996383109</v>
+        <v>223.3145040557498</v>
       </c>
       <c r="F12" t="n">
         <v>1.347263416903578</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3495205522225554</v>
+        <v>0.3495205522225553</v>
       </c>
       <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.38578869047619</v>
+      </c>
+      <c r="J12" t="n">
+        <v>17.61904761904762</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.478143601190476</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>17.61904761904762</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.28794642857143</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9.151785714285714</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.735119047619047</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.519345238095238</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.6293826219512195</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.9024390243902439</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.7659108231707317</v>
+      <c r="AA12" t="n">
+        <v>2.602306547619047</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.38578869047619</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>18.50991177721088</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1481,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.600832837596669</v>
+        <v>2516.09977324263</v>
       </c>
       <c r="D13" t="n">
-        <v>15.45886022288625</v>
+        <v>301.8158424468268</v>
       </c>
       <c r="E13" t="n">
-        <v>11.52133344150171</v>
+        <v>224.9403195721762</v>
       </c>
       <c r="F13" t="n">
         <v>1.341759641049961</v>
@@ -1026,16 +1500,60 @@
         <v>0.3470992361426351</v>
       </c>
       <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.026785714285714</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18.09523809523809</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.548363095238095</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.926829268292683</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.6898818597560976</v>
+      <c r="M13" t="n">
+        <v>18.09523809523809</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12.31212797619048</v>
+      </c>
+      <c r="O13" t="n">
+        <v>10</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.722098214285714</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.664434523809524</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.994791666666667</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.026785714285714</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>12.78526254251701</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1564,76 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.60261748958953</v>
+        <v>2516.780045351474</v>
       </c>
       <c r="D14" t="n">
-        <v>15.49580462385969</v>
+        <v>302.5371378944034</v>
       </c>
       <c r="E14" t="n">
-        <v>11.63909998172667</v>
+        <v>227.2395710718064</v>
       </c>
       <c r="F14" t="n">
         <v>1.33135763488483</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3455395297997611</v>
+        <v>0.345539529799761</v>
       </c>
       <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.927827380952381</v>
+      </c>
+      <c r="J14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.445737670068025</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.5121951219512195</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.7090002540650406</v>
+      <c r="M14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="N14" t="n">
+        <v>12.95572916666667</v>
+      </c>
+      <c r="O14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.996651785714286</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.33891369047619</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.329613095238095</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.927827380952381</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>10.05022321428572</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1644,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.598750743604997</v>
+        <v>2515.306122448979</v>
       </c>
       <c r="D15" t="n">
-        <v>15.56233925935699</v>
+        <v>303.8361474445888</v>
       </c>
       <c r="E15" t="n">
-        <v>11.61644307287728</v>
+        <v>226.7972218990326</v>
       </c>
       <c r="F15" t="n">
         <v>1.339681963035037</v>
@@ -1104,16 +1663,54 @@
         <v>0.3423905980364002</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6693025914634146</v>
+        <v>3.309151785714286</v>
       </c>
       <c r="J15" t="n">
-        <v>0.951219512195122</v>
+        <v>18.57142857142857</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8102610518292683</v>
+        <v>8.639987244897959</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="N15" t="n">
+        <v>13.06733630952381</v>
+      </c>
+      <c r="O15" t="n">
+        <v>9.691220238095237</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.309151785714286</v>
+      </c>
+      <c r="X15" t="n">
+        <v>7.989211309523809</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.787481398809524</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>9.928075396825397</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1721,76 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.553242117787032</v>
+        <v>2497.959183673469</v>
       </c>
       <c r="D16" t="n">
-        <v>15.28047711093251</v>
+        <v>298.3331245467776</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4868404603586</v>
+        <v>224.2668851784297</v>
       </c>
       <c r="F16" t="n">
         <v>1.330259366243125</v>
       </c>
       <c r="G16" t="n">
-        <v>0.352689271075942</v>
+        <v>0.3526892710759419</v>
       </c>
       <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.786458333333333</v>
+      </c>
+      <c r="J16" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8.258928571428571</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.693407012195122</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.822313262195122</v>
+      <c r="M16" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="N16" t="n">
+        <v>13.53794642857143</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>9.347098214285714</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7.555803571428571</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.046875</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.966889880952381</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.786458333333333</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>18.2555183531746</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1801,76 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.530339083878644</v>
+        <v>2489.22902494331</v>
       </c>
       <c r="D17" t="n">
-        <v>15.26965632671263</v>
+        <v>298.1218616167704</v>
       </c>
       <c r="E17" t="n">
-        <v>11.57358064884093</v>
+        <v>225.9603840964181</v>
       </c>
       <c r="F17" t="n">
         <v>1.319354553272315</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3519549448770772</v>
+        <v>0.3519549448770773</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6926448170731707</v>
+        <v>2.289806547619047</v>
       </c>
       <c r="J17" t="n">
-        <v>0.951219512195122</v>
+        <v>18.57142857142857</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8219321646341464</v>
+        <v>8.216943027210885</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="N17" t="n">
+        <v>13.52306547619048</v>
+      </c>
+      <c r="O17" t="n">
+        <v>9.74516369047619</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7.7734375</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.829241071428571</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.786458333333333</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.289806547619047</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>12.67554873511905</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1881,76 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.446757882212969</v>
+        <v>2457.369614512471</v>
       </c>
       <c r="D18" t="n">
-        <v>15.13760234960696</v>
+        <v>295.5436649208977</v>
       </c>
       <c r="E18" t="n">
-        <v>11.42723919124138</v>
+        <v>223.1032413528079</v>
       </c>
       <c r="F18" t="n">
         <v>1.32469462625841</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3535387636688182</v>
+        <v>0.3535387636688181</v>
       </c>
       <c r="H18" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.315104166666667</v>
+      </c>
+      <c r="J18" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.833758503401362</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.6758765243902439</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.951219512195122</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.813548018292683</v>
+      <c r="M18" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="N18" t="n">
+        <v>13.19568452380952</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8.803943452380953</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7.581845238095237</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.011532738095238</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.356770833333333</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.315104166666667</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +1961,76 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.370315288518739</v>
+        <v>2428.231292517007</v>
       </c>
       <c r="D19" t="n">
-        <v>15.05086213786428</v>
+        <v>293.8501655487787</v>
       </c>
       <c r="E19" t="n">
-        <v>11.28334907787602</v>
+        <v>220.2939581871033</v>
       </c>
       <c r="F19" t="n">
         <v>1.333900248408999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3533849388877926</v>
+        <v>0.3533849388877927</v>
       </c>
       <c r="H19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9933035714285714</v>
+      </c>
+      <c r="J19" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.776360544217686</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6751143292682927</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.975609756097561</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.8253620426829269</v>
+      <c r="M19" t="n">
+        <v>19.04761904761905</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13.18080357142857</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8.346354166666666</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7.397693452380952</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.754836309523809</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.71391369047619</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.9933035714285714</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>7.190848214285714</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2041,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.169541939321832</v>
+        <v>2351.700680272108</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79267222125356</v>
+        <v>288.8093147959028</v>
       </c>
       <c r="E20" t="n">
-        <v>11.10843266801136</v>
+        <v>216.8789235183171</v>
       </c>
       <c r="F20" t="n">
         <v>1.331661510075278</v>
@@ -1299,16 +2060,57 @@
         <v>0.3542986654667504</v>
       </c>
       <c r="H20" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19.52380952380952</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.486447704081632</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.6341463414634146</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.8170731707317074</v>
+      <c r="M20" t="n">
+        <v>19.52380952380952</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12.38095238095238</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7.524181547619047</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6.508556547619047</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.8125</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.613467261904762</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>5.152529761904761</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2121,76 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.867638310529447</v>
+        <v>2236.621315192744</v>
       </c>
       <c r="D21" t="n">
-        <v>14.73797366386507</v>
+        <v>287.7413905802227</v>
       </c>
       <c r="E21" t="n">
-        <v>10.93596758784317</v>
+        <v>213.5117481436048</v>
       </c>
       <c r="F21" t="n">
         <v>1.347660693530981</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3394670663461837</v>
+        <v>0.3394670663461838</v>
       </c>
       <c r="H21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.240699404761905</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18.87834821428571</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.763392857142856</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.6829268292682927</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.9669397865853658</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.8249333079268293</v>
+      <c r="M21" t="n">
+        <v>18.87834821428571</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6.010044642857142</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.240699404761905</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.779017857142857</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.185639880952381</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>3.504464285714286</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2200,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>3.309151785714286</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2222,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>7.989211309523809</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2239,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>4.787481398809524</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>2.744502314814815</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.266281512605042</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>1.815662202380953</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.240699404761905</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>2.779017857142857</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>2.185639880952381</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/29/Filled_2D_sections/coronal/week29_coronal_Batch_Allmarks.xlsx
+++ b/measurements/29/Filled_2D_sections/coronal/week29_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2358,4 +2564,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week29_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2496.768707482993</v>
+      </c>
+      <c r="D10" t="n">
+        <v>79.40433874599083</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2236.621315192744</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2584.467120181406</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>306.3706902804828</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14.39270346836115</v>
+      </c>
+      <c r="E11" t="n">
+        <v>283.5373778002602</v>
+      </c>
+      <c r="F11" t="n">
+        <v>329.6379407246907</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.375409813240295</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06034503842516062</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.275778365885707</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.47656276066279</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3358723979844039</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.02762496986182885</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.293550072732533</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4039803472837746</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0123.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0129.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0133.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.5871429486123998</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.7591546545162482</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.136708081768532</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.8870412083230169</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>61</v>
+      </c>
+      <c r="C48" t="n">
+        <v>13.6524199843872</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.665972703140288</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.523809523809524</v>
+      </c>
+      <c r="F48" t="n">
+        <v>20.47619047619047</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>33</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.884965728715729</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.153903191942564</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.309151785714286</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.347098214285714</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.34340834548105</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5846851853424281</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9933035714285714</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.046875</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>